--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M319"/>
+  <dimension ref="A1:M318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>599999.4</v>
+        <v>644.49</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9447750</v>
+        <v>10148.29</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8998935.65</v>
+        <v>9666.190000000001</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>28086800.45</v>
+        <v>30169.39</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2894999.37</v>
+        <v>3109.66</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>551999.78</v>
+        <v>592.9299999999999</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16659999.67</v>
+        <v>17895.31</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>99874.45</v>
+        <v>107.28</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>34045932.01</v>
+        <v>36570.39</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>29399999.96</v>
+        <v>31579.96</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8933092</v>
+        <v>9595.469999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>73499999.90000001</v>
+        <v>78949.91</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>368000.24</v>
+        <v>395.29</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15999097.8</v>
+        <v>17185.41</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>14070545.86</v>
+        <v>15113.86</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8545991.74</v>
+        <v>9179.66</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5896072.79</v>
+        <v>6333.26</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>305760.15</v>
+        <v>328.43</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>470399.6</v>
+        <v>505.28</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1104460.21</v>
+        <v>1186.35</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4844515.5</v>
+        <v>5203.73</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1300000.46</v>
+        <v>1396.39</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>570000</v>
+        <v>612.26</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7795900.06</v>
+        <v>8373.950000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3132370</v>
+        <v>3364.63</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>405719.81</v>
+        <v>435.8</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5981332.51</v>
+        <v>6424.84</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>22789312.46</v>
+        <v>24479.11</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5217029.52</v>
+        <v>5603.86</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6298015.5</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5415166</v>
+        <v>5816.69</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>784000.11</v>
+        <v>842.13</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7839999.91</v>
+        <v>8421.32</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>99999.85000000001</v>
+        <v>107.41</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>19000000</v>
+        <v>20408.82</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>140750907.77</v>
+        <v>151187.37</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1078979.9</v>
+        <v>1158.98</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>800000.37</v>
+        <v>859.3200000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2547384.31</v>
+        <v>2736.27</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>800000.37</v>
+        <v>859.3200000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1344559.79</v>
+        <v>1444.26</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6800219.49</v>
+        <v>7304.45</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>15058679.95</v>
+        <v>16175.26</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5000000.87</v>
+        <v>5370.74</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4878047.83</v>
+        <v>5239.75</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>914300.8</v>
+        <v>982.09</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>22699250.33</v>
+        <v>24382.36</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>53938219.41</v>
+        <v>57937.66</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>665616.8100000001</v>
+        <v>714.97</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>42542976</v>
+        <v>45697.47</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>466480</v>
+        <v>501.07</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10444840.56</v>
+        <v>11219.31</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3207050</v>
+        <v>3444.85</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>475000</v>
+        <v>510.22</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1235000</v>
+        <v>1326.57</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>29700000.25</v>
+        <v>31902.21</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7641063.75</v>
+        <v>8207.639999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7306607.7</v>
+        <v>7848.38</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>583100</v>
+        <v>626.34</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1500000.26</v>
+        <v>1611.22</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6972699.3</v>
+        <v>7489.71</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>63688240.34</v>
+        <v>68410.63</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17493000</v>
+        <v>18790.08</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>40999277.06</v>
+        <v>44039.31</v>
       </c>
     </row>
     <row r="66">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>688749999.28</v>
+        <v>739819.76</v>
       </c>
     </row>
     <row r="67">
@@ -4534,11 +4534,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>69076800.39</v>
+        <v>74198.74000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4595,11 +4595,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9219100.220000001</v>
+        <v>9902.68</v>
       </c>
     </row>
     <row r="69">
@@ -4656,11 +4656,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11662000</v>
+        <v>12526.72</v>
       </c>
     </row>
     <row r="70">
@@ -4717,11 +4717,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>14504495.88</v>
+        <v>15579.98</v>
       </c>
     </row>
     <row r="71">
@@ -4778,11 +4778,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3213001.12</v>
+        <v>3451.24</v>
       </c>
     </row>
     <row r="72">
@@ -4839,11 +4839,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5982899.88</v>
+        <v>6426.52</v>
       </c>
     </row>
     <row r="73">
@@ -4900,11 +4900,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>27859832.27</v>
+        <v>29925.6</v>
       </c>
     </row>
     <row r="74">
@@ -4961,11 +4961,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15689649</v>
+        <v>16853.01</v>
       </c>
     </row>
     <row r="75">
@@ -5022,11 +5022,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>70000000.45999999</v>
+        <v>75190.39</v>
       </c>
     </row>
     <row r="76">
@@ -5083,11 +5083,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>17140200.01</v>
+        <v>18411.12</v>
       </c>
     </row>
     <row r="77">
@@ -5144,11 +5144,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>20050211.87</v>
+        <v>21536.9</v>
       </c>
     </row>
     <row r="78">
@@ -5205,11 +5205,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11177880.06</v>
+        <v>12006.7</v>
       </c>
     </row>
     <row r="79">
@@ -5266,11 +5266,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>98686.17999999999</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80">
@@ -5327,11 +5327,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4898922.81</v>
+        <v>5262.17</v>
       </c>
     </row>
     <row r="81">
@@ -5388,11 +5388,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>205800.48</v>
+        <v>221.06</v>
       </c>
     </row>
     <row r="82">
@@ -5449,11 +5449,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>34984515.43</v>
+        <v>37578.56</v>
       </c>
     </row>
     <row r="83">
@@ -5510,11 +5510,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>45069710.4</v>
+        <v>48411.56</v>
       </c>
     </row>
     <row r="84">
@@ -5571,11 +5571,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1825000.37</v>
+        <v>1960.32</v>
       </c>
     </row>
     <row r="85">
@@ -5632,11 +5632,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>12000000.91</v>
+        <v>12889.78</v>
       </c>
     </row>
     <row r="86">
@@ -5693,11 +5693,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>19355000.4</v>
+        <v>20790.14</v>
       </c>
     </row>
     <row r="87">
@@ -5754,11 +5754,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>14815999.56</v>
+        <v>15914.58</v>
       </c>
     </row>
     <row r="88">
@@ -5815,11 +5815,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>20767670.94</v>
+        <v>22307.56</v>
       </c>
     </row>
     <row r="89">
@@ -5876,11 +5876,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1000000.17</v>
+        <v>1074.15</v>
       </c>
     </row>
     <row r="90">
@@ -5937,11 +5937,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>245012.6</v>
+        <v>263.18</v>
       </c>
     </row>
     <row r="91">
@@ -5998,11 +5998,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>17493000</v>
+        <v>18790.08</v>
       </c>
     </row>
     <row r="92">
@@ -6059,11 +6059,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>150000</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="93">
@@ -6124,11 +6124,11 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>236716708.76</v>
+        <v>254268.89</v>
       </c>
     </row>
     <row r="94">
@@ -6185,11 +6185,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4750000</v>
+        <v>5102.21</v>
       </c>
     </row>
     <row r="95">
@@ -6246,11 +6246,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5270531</v>
+        <v>5661.33</v>
       </c>
     </row>
     <row r="96">
@@ -6307,11 +6307,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2490900</v>
+        <v>2675.6</v>
       </c>
     </row>
     <row r="97">
@@ -6368,11 +6368,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2850000</v>
+        <v>3061.32</v>
       </c>
     </row>
     <row r="98">
@@ -6429,11 +6429,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7555825</v>
+        <v>8116.08</v>
       </c>
     </row>
     <row r="99">
@@ -6490,11 +6490,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>24116956.5</v>
+        <v>25905.19</v>
       </c>
     </row>
     <row r="100">
@@ -6551,11 +6551,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>9325680.4</v>
+        <v>10017.17</v>
       </c>
     </row>
     <row r="101">
@@ -6612,11 +6612,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5524259.08</v>
+        <v>5933.87</v>
       </c>
     </row>
     <row r="102">
@@ -6673,11 +6673,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3678920.18</v>
+        <v>3951.71</v>
       </c>
     </row>
     <row r="103">
@@ -6734,11 +6734,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>13715099.76</v>
+        <v>14732.05</v>
       </c>
     </row>
     <row r="104">
@@ -6795,11 +6795,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>258313.3</v>
+        <v>277.47</v>
       </c>
     </row>
     <row r="105">
@@ -6856,11 +6856,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>14342928.05</v>
+        <v>15406.43</v>
       </c>
     </row>
     <row r="106">
@@ -6917,11 +6917,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1884539.55</v>
+        <v>2024.28</v>
       </c>
     </row>
     <row r="107">
@@ -6978,11 +6978,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>42459872.59</v>
+        <v>45608.21</v>
       </c>
     </row>
     <row r="108">
@@ -7039,11 +7039,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>13245482.69</v>
+        <v>14227.61</v>
       </c>
     </row>
     <row r="109">
@@ -7100,11 +7100,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4025000</v>
+        <v>4323.45</v>
       </c>
     </row>
     <row r="110">
@@ -7161,11 +7161,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>299999.65</v>
+        <v>322.24</v>
       </c>
     </row>
     <row r="111">
@@ -7222,11 +7222,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>900000.86</v>
+        <v>966.73</v>
       </c>
     </row>
     <row r="112">
@@ -7283,11 +7283,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>14029679.88</v>
+        <v>15069.96</v>
       </c>
     </row>
     <row r="113">
@@ -7344,11 +7344,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2499999.27</v>
+        <v>2685.37</v>
       </c>
     </row>
     <row r="114">
@@ -7405,11 +7405,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>11245596.5</v>
+        <v>12079.44</v>
       </c>
     </row>
     <row r="115">
@@ -7466,11 +7466,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2864926.57</v>
+        <v>3077.36</v>
       </c>
     </row>
     <row r="116">
@@ -7527,11 +7527,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>10794347.2</v>
+        <v>11594.73</v>
       </c>
     </row>
     <row r="117">
@@ -7588,11 +7588,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>14165899.04</v>
+        <v>15216.28</v>
       </c>
     </row>
     <row r="118">
@@ -7649,11 +7649,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4875624.47</v>
+        <v>5237.14</v>
       </c>
     </row>
     <row r="119">
@@ -7710,11 +7710,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5000000.87</v>
+        <v>5370.74</v>
       </c>
     </row>
     <row r="120">
@@ -7771,11 +7771,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>26589360</v>
+        <v>28560.92</v>
       </c>
     </row>
     <row r="121">
@@ -7832,11 +7832,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>13179602.88</v>
+        <v>14156.85</v>
       </c>
     </row>
     <row r="122">
@@ -7893,11 +7893,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8454950</v>
+        <v>9081.870000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7954,11 +7954,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>29672775</v>
+        <v>31872.97</v>
       </c>
     </row>
     <row r="124">
@@ -8015,11 +8015,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1900000</v>
+        <v>2040.88</v>
       </c>
     </row>
     <row r="125">
@@ -8076,11 +8076,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>20641740</v>
+        <v>22172.29</v>
       </c>
     </row>
     <row r="126">
@@ -8137,11 +8137,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>529200.5699999999</v>
+        <v>568.4400000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8198,11 +8198,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>685020.05</v>
+        <v>735.8099999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8259,11 +8259,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1914250</v>
+        <v>2056.19</v>
       </c>
     </row>
     <row r="129">
@@ -8320,11 +8320,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3013347.75</v>
+        <v>3236.78</v>
       </c>
     </row>
     <row r="130">
@@ -8381,11 +8381,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>39449410.09</v>
+        <v>42374.52</v>
       </c>
     </row>
     <row r="131">
@@ -8442,11 +8442,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>285000</v>
+        <v>306.13</v>
       </c>
     </row>
     <row r="132">
@@ -8503,11 +8503,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>17498879.98</v>
+        <v>18796.4</v>
       </c>
     </row>
     <row r="133">
@@ -8564,11 +8564,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>25613279.76</v>
+        <v>27512.47</v>
       </c>
     </row>
     <row r="134">
@@ -8625,11 +8625,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>39063987.99</v>
+        <v>41960.52</v>
       </c>
     </row>
     <row r="135">
@@ -8686,11 +8686,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2064213.65</v>
+        <v>2217.27</v>
       </c>
     </row>
     <row r="136">
@@ -8747,11 +8747,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1823309.38</v>
+        <v>1958.5</v>
       </c>
     </row>
     <row r="137">
@@ -8808,11 +8808,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>38000000</v>
+        <v>40817.64</v>
       </c>
     </row>
     <row r="138">
@@ -8869,11 +8869,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>360000.11</v>
+        <v>386.69</v>
       </c>
     </row>
     <row r="139">
@@ -8930,11 +8930,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>28724779.49</v>
+        <v>30854.68</v>
       </c>
     </row>
     <row r="140">
@@ -8991,11 +8991,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>803511.8</v>
+        <v>863.09</v>
       </c>
     </row>
     <row r="141">
@@ -9052,11 +9052,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>438284.4</v>
+        <v>470.78</v>
       </c>
     </row>
     <row r="142">
@@ -9113,11 +9113,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>999433.4</v>
+        <v>1073.54</v>
       </c>
     </row>
     <row r="143">
@@ -9174,11 +9174,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5880000.23</v>
+        <v>6315.99</v>
       </c>
     </row>
     <row r="144">
@@ -9235,11 +9235,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>8631840.380000001</v>
+        <v>9271.879999999999</v>
       </c>
     </row>
     <row r="145">
@@ -9296,11 +9296,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>6588839.91</v>
+        <v>7077.39</v>
       </c>
     </row>
     <row r="146">
@@ -9357,11 +9357,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>13500000.01</v>
+        <v>14501</v>
       </c>
     </row>
     <row r="147">
@@ -9418,11 +9418,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>299999.55</v>
+        <v>322.24</v>
       </c>
     </row>
     <row r="148">
@@ -9479,11 +9479,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>15323770.04</v>
+        <v>16460</v>
       </c>
     </row>
     <row r="149">
@@ -9540,11 +9540,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>40850319.5</v>
+        <v>43879.31</v>
       </c>
     </row>
     <row r="150">
@@ -9601,11 +9601,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>9562840</v>
+        <v>10271.91</v>
       </c>
     </row>
     <row r="151">
@@ -9662,11 +9662,11 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3484000</v>
+        <v>3742.33</v>
       </c>
     </row>
     <row r="152">
@@ -9723,11 +9723,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>12984019.48</v>
+        <v>13946.76</v>
       </c>
     </row>
     <row r="153">
@@ -9784,11 +9784,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>266206.14</v>
+        <v>285.94</v>
       </c>
     </row>
     <row r="154">
@@ -9845,11 +9845,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>11577719.89</v>
+        <v>12436.19</v>
       </c>
     </row>
     <row r="155">
@@ -9906,11 +9906,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>52081120.55</v>
+        <v>55942.86</v>
       </c>
     </row>
     <row r="156">
@@ -9967,11 +9967,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>25172999.6</v>
+        <v>27039.54</v>
       </c>
     </row>
     <row r="157">
@@ -10028,11 +10028,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>6747299.67</v>
+        <v>7247.6</v>
       </c>
     </row>
     <row r="158">
@@ -10089,11 +10089,11 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>24028620.37</v>
+        <v>25810.31</v>
       </c>
     </row>
     <row r="159">
@@ -10150,11 +10150,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2997134</v>
+        <v>3219.37</v>
       </c>
     </row>
     <row r="160">
@@ -10211,11 +10211,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2939999.53</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="161">
@@ -10272,11 +10272,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>9012079.890000001</v>
+        <v>9680.309999999999</v>
       </c>
     </row>
     <row r="162">
@@ -10333,11 +10333,11 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>149998.98</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="163">
@@ -10394,11 +10394,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>13400804.2</v>
+        <v>14394.45</v>
       </c>
     </row>
     <row r="164">
@@ -10455,11 +10455,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>9613799.439999999</v>
+        <v>10326.65</v>
       </c>
     </row>
     <row r="165">
@@ -10516,11 +10516,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>42096878.84</v>
+        <v>45218.3</v>
       </c>
     </row>
     <row r="166">
@@ -10577,11 +10577,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>22718359.69</v>
+        <v>24402.89</v>
       </c>
     </row>
     <row r="167">
@@ -10638,11 +10638,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>477719.84</v>
+        <v>513.14</v>
       </c>
     </row>
     <row r="168">
@@ -10699,11 +10699,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>17039259.57</v>
+        <v>18302.69</v>
       </c>
     </row>
     <row r="169">
@@ -10760,11 +10760,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>180000.64</v>
+        <v>193.35</v>
       </c>
     </row>
     <row r="170">
@@ -10821,11 +10821,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>10062547</v>
+        <v>10808.67</v>
       </c>
     </row>
     <row r="171">
@@ -10882,11 +10882,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>323400.09</v>
+        <v>347.38</v>
       </c>
     </row>
     <row r="172">
@@ -10943,11 +10943,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5089630.33</v>
+        <v>5467.02</v>
       </c>
     </row>
     <row r="173">
@@ -11004,11 +11004,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>18927699.3</v>
+        <v>20331.16</v>
       </c>
     </row>
     <row r="174">
@@ -11065,11 +11065,11 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2199119.67</v>
+        <v>2362.18</v>
       </c>
     </row>
     <row r="175">
@@ -11126,11 +11126,11 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>29501430.21</v>
+        <v>31688.92</v>
       </c>
     </row>
     <row r="176">
@@ -11187,11 +11187,11 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>21000000</v>
+        <v>22557.12</v>
       </c>
     </row>
     <row r="177">
@@ -11248,11 +11248,11 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>254231.6</v>
+        <v>273.08</v>
       </c>
     </row>
     <row r="178">
@@ -11309,11 +11309,11 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>216600</v>
+        <v>232.66</v>
       </c>
     </row>
     <row r="179">
@@ -11370,11 +11370,11 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3060000</v>
+        <v>3286.89</v>
       </c>
     </row>
     <row r="180">
@@ -11431,11 +11431,11 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1908571.43</v>
+        <v>2050.09</v>
       </c>
     </row>
     <row r="181">
@@ -11492,11 +11492,11 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>319999.45</v>
+        <v>343.73</v>
       </c>
     </row>
     <row r="182">
@@ -11553,11 +11553,11 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>14177072.4</v>
+        <v>15228.28</v>
       </c>
     </row>
     <row r="183">
@@ -11614,11 +11614,11 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>149998.98</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="184">
@@ -11675,11 +11675,11 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3728341.4</v>
+        <v>4004.79</v>
       </c>
     </row>
     <row r="185">
@@ -11736,11 +11736,11 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>14368000.33</v>
+        <v>15433.37</v>
       </c>
     </row>
     <row r="186">
@@ -11797,11 +11797,11 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>43764369.91</v>
+        <v>47009.43</v>
       </c>
     </row>
     <row r="187">
@@ -11858,11 +11858,11 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2191422</v>
+        <v>2353.91</v>
       </c>
     </row>
     <row r="188">
@@ -11919,11 +11919,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>5947620</v>
+        <v>6388.63</v>
       </c>
     </row>
     <row r="189">
@@ -11980,11 +11980,11 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>6237420.7</v>
+        <v>6699.92</v>
       </c>
     </row>
     <row r="190">
@@ -12041,11 +12041,11 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>8152129.84</v>
+        <v>8756.6</v>
       </c>
     </row>
     <row r="191">
@@ -12102,11 +12102,11 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>341999.81</v>
+        <v>367.36</v>
       </c>
     </row>
     <row r="192">
@@ -12163,11 +12163,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>21763350.34</v>
+        <v>23377.07</v>
       </c>
     </row>
     <row r="193">
@@ -12224,11 +12224,11 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>285000</v>
+        <v>306.13</v>
       </c>
     </row>
     <row r="194">
@@ -12285,11 +12285,11 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>13873860.4</v>
+        <v>14902.59</v>
       </c>
     </row>
     <row r="195">
@@ -12346,11 +12346,11 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3816666</v>
+        <v>4099.67</v>
       </c>
     </row>
     <row r="196">
@@ -12407,11 +12407,11 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4760000.4</v>
+        <v>5112.95</v>
       </c>
     </row>
     <row r="197">
@@ -12468,11 +12468,11 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>285000</v>
+        <v>306.13</v>
       </c>
     </row>
     <row r="198">
@@ -12529,11 +12529,11 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>25000995.6</v>
+        <v>26854.78</v>
       </c>
     </row>
     <row r="199">
@@ -12590,11 +12590,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>553945</v>
+        <v>595.02</v>
       </c>
     </row>
     <row r="200">
@@ -12651,11 +12651,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>17690371.19</v>
+        <v>19002.09</v>
       </c>
     </row>
     <row r="201">
@@ -12712,11 +12712,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2550000</v>
+        <v>2739.08</v>
       </c>
     </row>
     <row r="202">
@@ -12773,11 +12773,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>199999.8</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="203">
@@ -12834,11 +12834,11 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>15738799.63</v>
+        <v>16905.81</v>
       </c>
     </row>
     <row r="204">
@@ -12895,11 +12895,11 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>11297440.05</v>
+        <v>12135.13</v>
       </c>
     </row>
     <row r="205">
@@ -12956,11 +12956,11 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>800000.37</v>
+        <v>859.3200000000001</v>
       </c>
     </row>
     <row r="206">
@@ -13017,11 +13017,11 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>14242514.88</v>
+        <v>15298.58</v>
       </c>
     </row>
     <row r="207">
@@ -13078,11 +13078,11 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>39090239.15</v>
+        <v>41988.72</v>
       </c>
     </row>
     <row r="208">
@@ -13139,11 +13139,11 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>61750</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="209">
@@ -13200,11 +13200,11 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>190000</v>
+        <v>204.09</v>
       </c>
     </row>
     <row r="210">
@@ -13261,11 +13261,11 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2008000.48</v>
+        <v>2156.89</v>
       </c>
     </row>
     <row r="211">
@@ -13322,11 +13322,11 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>31016772.99</v>
+        <v>33316.62</v>
       </c>
     </row>
     <row r="212">
@@ -13383,11 +13383,11 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>12000000.91</v>
+        <v>12889.78</v>
       </c>
     </row>
     <row r="213">
@@ -13444,11 +13444,11 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>19415759.42</v>
+        <v>20855.41</v>
       </c>
     </row>
     <row r="214">
@@ -13505,11 +13505,11 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>152000</v>
+        <v>163.27</v>
       </c>
     </row>
     <row r="215">
@@ -13566,11 +13566,11 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>15455000.19</v>
+        <v>16600.96</v>
       </c>
     </row>
     <row r="216">
@@ -13627,11 +13627,11 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3567199.38</v>
+        <v>3831.7</v>
       </c>
     </row>
     <row r="217">
@@ -13688,11 +13688,11 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>748949.97</v>
+        <v>804.48</v>
       </c>
     </row>
     <row r="218">
@@ -13749,11 +13749,11 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>249998.29</v>
+        <v>268.54</v>
       </c>
     </row>
     <row r="219">
@@ -13810,11 +13810,11 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>546000.85</v>
+        <v>586.49</v>
       </c>
     </row>
     <row r="220">
@@ -13871,11 +13871,11 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3692100</v>
+        <v>3965.86</v>
       </c>
     </row>
     <row r="221">
@@ -13932,11 +13932,11 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4760000</v>
+        <v>5112.95</v>
       </c>
     </row>
     <row r="222">
@@ -13993,11 +13993,11 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>182280.56</v>
+        <v>195.8</v>
       </c>
     </row>
     <row r="223">
@@ -14054,11 +14054,11 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>11760194.04</v>
+        <v>12632.19</v>
       </c>
     </row>
     <row r="224">
@@ -14115,11 +14115,11 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>9102051.060000001</v>
+        <v>9776.950000000001</v>
       </c>
     </row>
     <row r="225">
@@ -14176,11 +14176,11 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>9643200.51</v>
+        <v>10358.23</v>
       </c>
     </row>
     <row r="226">
@@ -14237,11 +14237,11 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>527938.74</v>
+        <v>567.08</v>
       </c>
     </row>
     <row r="227">
@@ -14298,11 +14298,11 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1700000.3</v>
+        <v>1826.05</v>
       </c>
     </row>
     <row r="228">
@@ -14359,11 +14359,11 @@
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1274000.03</v>
+        <v>1368.47</v>
       </c>
     </row>
     <row r="229">
@@ -14420,11 +14420,11 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2005864</v>
+        <v>2154.6</v>
       </c>
     </row>
     <row r="230">
@@ -14481,11 +14481,11 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>240237.2</v>
+        <v>258.05</v>
       </c>
     </row>
     <row r="231">
@@ -14542,11 +14542,11 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>33406500.15</v>
+        <v>35883.54</v>
       </c>
     </row>
     <row r="232">
@@ -14603,11 +14603,11 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>35000000.23</v>
+        <v>37595.2</v>
       </c>
     </row>
     <row r="233">
@@ -14664,11 +14664,11 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>5439000.53</v>
+        <v>5842.29</v>
       </c>
     </row>
     <row r="234">
@@ -14725,11 +14725,11 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>20864199.65</v>
+        <v>22411.25</v>
       </c>
     </row>
     <row r="235">
@@ -14786,11 +14786,11 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>42000000.28</v>
+        <v>45114.24</v>
       </c>
     </row>
     <row r="236">
@@ -14847,11 +14847,11 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1000000</v>
+        <v>1074.15</v>
       </c>
     </row>
     <row r="237">
@@ -14908,11 +14908,11 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1500000.26</v>
+        <v>1611.22</v>
       </c>
     </row>
     <row r="238">
@@ -14969,11 +14969,11 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>20000001.13</v>
+        <v>21482.97</v>
       </c>
     </row>
     <row r="239">
@@ -15030,11 +15030,11 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1440000.44</v>
+        <v>1546.77</v>
       </c>
     </row>
     <row r="240">
@@ -15091,11 +15091,11 @@
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>23000000.49</v>
+        <v>24705.42</v>
       </c>
     </row>
     <row r="241">
@@ -15152,11 +15152,11 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>9079699.67</v>
+        <v>9752.950000000001</v>
       </c>
     </row>
     <row r="242">
@@ -15213,11 +15213,11 @@
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2076227.84</v>
+        <v>2230.18</v>
       </c>
     </row>
     <row r="243">
@@ -15274,11 +15274,11 @@
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>16616389.62</v>
+        <v>17848.47</v>
       </c>
     </row>
     <row r="244">
@@ -15335,11 +15335,11 @@
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>6552278.37</v>
+        <v>7038.12</v>
       </c>
     </row>
     <row r="245">
@@ -15396,11 +15396,11 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>24649086.59</v>
+        <v>26476.78</v>
       </c>
     </row>
     <row r="246">
@@ -15457,11 +15457,11 @@
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>17890022.29</v>
+        <v>19216.54</v>
       </c>
     </row>
     <row r="247">
@@ -15518,11 +15518,11 @@
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>701190.58</v>
+        <v>753.1799999999999</v>
       </c>
     </row>
     <row r="248">
@@ -15579,11 +15579,11 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>11545380</v>
+        <v>12401.45</v>
       </c>
     </row>
     <row r="249">
@@ -15644,11 +15644,11 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>74065123.5999696</v>
+        <v>79556.94</v>
       </c>
     </row>
     <row r="250">
@@ -15705,11 +15705,11 @@
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>22193365.15</v>
+        <v>23838.97</v>
       </c>
     </row>
     <row r="251">
@@ -15766,11 +15766,11 @@
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>29399999.96</v>
+        <v>31579.96</v>
       </c>
     </row>
     <row r="252">
@@ -15827,11 +15827,11 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>899997.36</v>
+        <v>966.73</v>
       </c>
     </row>
     <row r="253">
@@ -15888,11 +15888,11 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>10858399.57</v>
+        <v>11663.53</v>
       </c>
     </row>
     <row r="254">
@@ -15949,11 +15949,11 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1425000</v>
+        <v>1530.66</v>
       </c>
     </row>
     <row r="255">
@@ -16010,11 +16010,11 @@
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>10000165</v>
+        <v>10741.66</v>
       </c>
     </row>
     <row r="256">
@@ -16071,11 +16071,11 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>13744002.87</v>
+        <v>14763.1</v>
       </c>
     </row>
     <row r="257">
@@ -16132,11 +16132,11 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3280000</v>
+        <v>3523.21</v>
       </c>
     </row>
     <row r="258">
@@ -16193,11 +16193,11 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1500000.26</v>
+        <v>1611.22</v>
       </c>
     </row>
     <row r="259">
@@ -16254,11 +16254,11 @@
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4163999.9</v>
+        <v>4472.75</v>
       </c>
     </row>
     <row r="260">
@@ -16315,11 +16315,11 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>16889192.95</v>
+        <v>18141.5</v>
       </c>
     </row>
     <row r="261">
@@ -16376,11 +16376,11 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>35240898.67</v>
+        <v>37853.96</v>
       </c>
     </row>
     <row r="262">
@@ -16437,11 +16437,11 @@
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3125500</v>
+        <v>3357.25</v>
       </c>
     </row>
     <row r="263">
@@ -16498,11 +16498,11 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>13720000.14</v>
+        <v>14737.32</v>
       </c>
     </row>
     <row r="264">
@@ -16559,11 +16559,11 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>34807500.26</v>
+        <v>37388.42</v>
       </c>
     </row>
     <row r="265">
@@ -16620,11 +16620,11 @@
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>11274024.3</v>
+        <v>12109.98</v>
       </c>
     </row>
     <row r="266">
@@ -16681,11 +16681,11 @@
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>8500000.310000001</v>
+        <v>9130.26</v>
       </c>
     </row>
     <row r="267">
@@ -16742,11 +16742,11 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>39999999.93</v>
+        <v>42965.94</v>
       </c>
     </row>
     <row r="268">
@@ -16803,11 +16803,11 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>29465071.59</v>
+        <v>31649.86</v>
       </c>
     </row>
     <row r="269">
@@ -16864,11 +16864,11 @@
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>69949523.83</v>
+        <v>75136.17</v>
       </c>
     </row>
     <row r="270">
@@ -16925,11 +16925,11 @@
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>48697019.23</v>
+        <v>52307.83</v>
       </c>
     </row>
     <row r="271">
@@ -16986,11 +16986,11 @@
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>25092689.15</v>
+        <v>26953.27</v>
       </c>
     </row>
     <row r="272">
@@ -17047,11 +17047,11 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>9096360</v>
+        <v>9770.84</v>
       </c>
     </row>
     <row r="273">
@@ -17108,11 +17108,11 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>30000000.53</v>
+        <v>32224.45</v>
       </c>
     </row>
     <row r="274">
@@ -17169,17 +17169,17 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>47125260.35</v>
+        <v>50619.53</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1978-767-CM26</t>
+          <t>1229788-160-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17199,48 +17199,48 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Solicitud de Cancelacion</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1138000</v>
+        <v>24022.66</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1229788-160-CM26</t>
+          <t>1395-590-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17291,17 +17291,17 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>22364376</v>
+        <v>42647.55</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1395-590-CM26</t>
+          <t>2378-251-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17326,43 +17326,43 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>39703591.54</v>
+        <v>2739.08</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2378-251-CM26</t>
+          <t>770-90-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17387,12 +17387,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>60.604.000-8</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17413,17 +17413,17 @@
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2550000</v>
+        <v>2142.92</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>770-90-CM26</t>
+          <t>3290-214-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17443,48 +17443,48 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>60.604.000-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1994993.35</v>
+        <v>18010.78</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3290-214-CM26</t>
+          <t>1681-561-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17509,43 +17509,43 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>16767499.98</v>
+        <v>38350.71</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1681-561-CM26</t>
+          <t>4360-71-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17560,27 +17560,27 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17596,17 +17596,17 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>35703361.11</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4360-71-CM26</t>
+          <t>539119-2494-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17657,17 +17657,17 @@
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>23067.9</v>
+        <v>7443.4</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>889473-1275-CM26</t>
+          <t>1622-998-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17692,12 +17692,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17718,17 +17718,17 @@
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>10301760.65</v>
+        <v>23631.27</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1622-998-CM26</t>
+          <t>1016-72-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17748,22 +17748,22 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17779,17 +17779,17 @@
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>22000000.31</v>
+        <v>1374.91</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1093870-11-CM26</t>
+          <t>4291-1122-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17814,17 +17814,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17840,17 +17840,17 @@
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>798000</v>
+        <v>8056.11</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>4291-1122-CM26</t>
+          <t>1464-1163-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17870,22 +17870,22 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17901,17 +17901,17 @@
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>7500000.13</v>
+        <v>37580.16</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1016-72-CM26</t>
+          <t>1093870-11-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17936,17 +17936,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17962,17 +17962,17 @@
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1279999.6</v>
+        <v>857.17</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1464-1163-CM26</t>
+          <t>1371-37-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17992,22 +17992,22 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>Comité de Seguro Agricola</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18023,17 +18023,17 @@
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>34986000</v>
+        <v>117.16</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1371-37-CM26</t>
+          <t>3281-60-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18053,48 +18053,48 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>109073.52</v>
+        <v>1628.47</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3281-60-CM26</t>
+          <t>3515-350-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18114,48 +18114,48 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1516060</v>
+        <v>7304.21</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3515-350-CM26</t>
+          <t>889473-1275-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18175,22 +18175,22 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18206,17 +18206,17 @@
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>6800000</v>
+        <v>11065.62</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>539119-2494-CM26</t>
+          <t>554892-5-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18241,17 +18241,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18267,17 +18267,17 @@
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>6929580.23</v>
+        <v>1421.1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>554892-5-CM26</t>
+          <t>1978-787-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18302,17 +18302,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18328,17 +18328,17 @@
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1323000.25</v>
+        <v>15789.98</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1978-787-CM26</t>
+          <t>898-2419-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18358,22 +18358,22 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18389,17 +18389,17 @@
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>14699999.98</v>
+        <v>20408.82</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>898-2419-CM26</t>
+          <t>1079454-324-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18419,22 +18419,22 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18450,17 +18450,17 @@
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>19000000.96</v>
+        <v>58926.64</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1079454-324-CM26</t>
+          <t>5605-6-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18480,22 +18480,22 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18511,17 +18511,17 @@
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>54858930.81</v>
+        <v>1020.44</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5605-6-CM26</t>
+          <t>1079563-312-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18541,48 +18541,48 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>950000</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1079563-312-CM26</t>
+          <t>45-185-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18607,43 +18607,43 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>200000</v>
+        <v>7237.11</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>45-185-CM26</t>
+          <t>2730-379-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18668,43 +18668,43 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>6737533</v>
+        <v>8893.950000000001</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2730-379-CM26</t>
+          <t>1057385-228-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18729,43 +18729,43 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>8280000</v>
+        <v>18947.98</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1057385-228-CM26</t>
+          <t>1978-786-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18790,17 +18790,17 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18816,17 +18816,17 @@
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>17639999.51</v>
+        <v>73686.58</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1978-786-CM26</t>
+          <t>1099834-88-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18846,22 +18846,22 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18877,17 +18877,17 @@
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>68599999.52</v>
+        <v>12889.78</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1099834-88-CM26</t>
+          <t>5349-1486-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -18912,17 +18912,17 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18938,17 +18938,17 @@
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>12000000.91</v>
+        <v>64998.18</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5349-1486-CM26</t>
+          <t>1480127-63-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18968,22 +18968,22 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -18999,17 +18999,17 @@
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>60511352.94</v>
+        <v>32111.87</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1480127-63-CM26</t>
+          <t>1057480-2191-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19034,12 +19034,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>Bienes y Servicios</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19060,17 +19060,17 @@
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>29895190.9</v>
+        <v>75190.39</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1057480-2191-CM26</t>
+          <t>2202-855-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19090,22 +19090,22 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19121,17 +19121,17 @@
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>70000000.45999999</v>
+        <v>315.8</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2202-855-CM26</t>
+          <t>5013-41-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19156,17 +19156,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>65.455.650-4</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19182,17 +19182,17 @@
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>293999.02</v>
+        <v>686.46</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5013-41-CM26</t>
+          <t>2146-385-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19217,43 +19217,43 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>65.455.650-4</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>639077.6</v>
+        <v>12887.17</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2146-385-CM26</t>
+          <t>1099899-129-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19278,43 +19278,43 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>11997565.89</v>
+        <v>7908.25</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1099899-129-CM26</t>
+          <t>1037834-12-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19334,22 +19334,22 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19365,17 +19365,17 @@
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>7362347.72</v>
+        <v>4253.63</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1037834-12-CM26</t>
+          <t>1013353-82-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19400,43 +19400,43 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>65.154.021-6</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3960000.03</v>
+        <v>3609.14</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1013353-82-CM26</t>
+          <t>5702-540-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19461,43 +19461,43 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>65.154.021-6</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3360000</v>
+        <v>429.66</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5702-540-CM26</t>
+          <t>4351-341-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19522,17 +19522,17 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19548,17 +19548,17 @@
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>400000</v>
+        <v>13833.24</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4351-341-CM26</t>
+          <t>1037834-11-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19583,17 +19583,17 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19609,17 +19609,17 @@
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>12878328.25</v>
+        <v>708.9400000000001</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1037834-11-CM26</t>
+          <t>620279-151-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19644,17 +19644,17 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.980.010-9</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>BASE NAVAL PUERTO MONTT</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19670,17 +19670,17 @@
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>660000.39</v>
+        <v>28317.4</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>620279-151-CM26</t>
+          <t>778998-131-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19705,17 +19705,17 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.980.010-9</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19731,17 +19731,17 @@
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>26362651.89</v>
+        <v>353.09</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>778998-131-CM26</t>
+          <t>1099899-128-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19761,22 +19761,22 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19792,17 +19792,17 @@
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>328720.29</v>
+        <v>1476.05</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1099899-128-CM26</t>
+          <t>2080-7563-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19822,22 +19822,22 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19853,72 +19853,11 @@
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1374155.62</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>2080-7563-CM26</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2239-1-LR26</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>61.602.138-9</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M319" s="2" t="n">
-        <v>12301099.76</v>
+        <v>13213.21</v>
       </c>
     </row>
   </sheetData>
